--- a/real_estate_forms/022_real_estate_referral_network_signup--real_estate_forms.xlsx
+++ b/real_estate_forms/022_real_estate_referral_network_signup--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,9 +440,9 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Partner Details</t>
+          <t>What is your real estate agency's name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>partner_location</t>
+          <t>partner_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>partner_location</t>
+          <t>What is your partner's name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>partner_phone</t>
+          <t>referral_method</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>partner_phone</t>
+          <t>How will you refer your partners?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>partner_email</t>
+          <t>partner_location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>partner_email</t>
+          <t>Is your partner's location in your service area?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,25 +612,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>partner_website</t>
+          <t>partner_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>partner_website</t>
+          <t>What is your partner's email address?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,30 +640,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Referral Terms</t>
+          <t>Do you agree with our referral terms?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>referral_terms_2</t>
+          <t>feedback_referral_terms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Referral Terms</t>
+          <t>Can you provide feedback on our referral terms?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,86 +676,86 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>referral_terms_3</t>
+          <t>confirm_contact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Referral Terms</t>
+          <t>Can you confirm your partner's contact details?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>referral_terms_4</t>
+          <t>partner_confirm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Referral Terms</t>
+          <t>Partner Confirm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>referral_terms_5</t>
+          <t>feedback_confusion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Referral Terms</t>
+          <t>Are you sure about our referral terms?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>referral_terms_6</t>
+          <t>additional_feedback</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Referral Terms</t>
+          <t>Additional Feedback</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,11 +776,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -804,170 +804,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>referral_terms_2_choices</t>
+          <t>referral_terms_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>referral_terms_2_choices</t>
+          <t>referral_terms_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>referral_terms_3_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>referral_terms_3_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>referral_terms_4_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>referral_terms_4_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>referral_terms_5_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>referral_terms_5_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>referral_terms_6_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>referral_terms_6_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
